--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,107 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44074</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43982</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43890</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43799</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43708</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43616</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -820,8 +824,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -885,8 +892,11 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -950,8 +960,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,55 +988,56 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E12" s="3">
         <v>9000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>400</v>
       </c>
       <c r="M12" s="3">
         <v>400</v>
       </c>
       <c r="N12" s="3">
+        <v>400</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
       <c r="P12" s="3">
         <v>0</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
+      <c r="R12" s="3">
+        <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
@@ -1040,8 +1054,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1122,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1170,8 +1190,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1258,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,61 +1283,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E17" s="3">
         <v>12100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>100</v>
       </c>
       <c r="U17" s="3">
         <v>100</v>
@@ -1322,8 +1349,11 @@
       <c r="W17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1331,52 +1361,52 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-100</v>
       </c>
       <c r="U18" s="3">
         <v>-100</v>
@@ -1387,8 +1417,11 @@
       <c r="W18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1445,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1421,35 +1455,35 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1457,16 +1491,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
       </c>
       <c r="T20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U20" s="3">
         <v>400</v>
@@ -1475,10 +1509,13 @@
         <v>400</v>
       </c>
       <c r="W20" s="3">
+        <v>400</v>
+      </c>
+      <c r="X20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1500,21 +1537,21 @@
       <c r="I21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1542,8 +1579,11 @@
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1553,8 +1593,8 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>4</v>
@@ -1565,8 +1605,8 @@
       <c r="I22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1578,11 +1618,11 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1598,8 +1638,8 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1607,61 +1647,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
-      </c>
-      <c r="T23" s="3">
-        <v>300</v>
       </c>
       <c r="U23" s="3">
         <v>300</v>
@@ -1672,8 +1715,11 @@
       <c r="W23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1710,8 +1756,8 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>4</v>
@@ -1728,8 +1774,8 @@
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1737,8 +1783,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,61 +1851,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
-      </c>
-      <c r="T26" s="3">
-        <v>300</v>
       </c>
       <c r="U26" s="3">
         <v>300</v>
@@ -1867,61 +1919,64 @@
       <c r="W26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>300</v>
       </c>
       <c r="U27" s="3">
         <v>300</v>
@@ -1932,8 +1987,11 @@
       <c r="W27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2055,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2123,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2191,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2259,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2201,35 +2271,35 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2237,16 +2307,16 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
       </c>
       <c r="T32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="U32" s="3">
         <v>-400</v>
@@ -2255,63 +2325,66 @@
         <v>-400</v>
       </c>
       <c r="W32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>300</v>
       </c>
       <c r="U33" s="3">
         <v>300</v>
@@ -2322,8 +2395,11 @@
       <c r="W33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,61 +2463,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>300</v>
       </c>
       <c r="U35" s="3">
         <v>300</v>
@@ -2452,78 +2531,84 @@
       <c r="W35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44074</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43982</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43890</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43799</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43708</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43616</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2632,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2658,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>35800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8800</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
       <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
-      </c>
-      <c r="R41" s="3">
-        <v>100</v>
       </c>
       <c r="S41" s="3">
         <v>100</v>
       </c>
       <c r="T41" s="3">
+        <v>100</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
-      </c>
-      <c r="U41" s="3">
-        <v>300</v>
       </c>
       <c r="V41" s="3">
         <v>300</v>
       </c>
       <c r="W41" s="3">
+        <v>300</v>
+      </c>
+      <c r="X41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,8 +2792,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2767,8 +2860,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,46 +2928,49 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -2880,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -2897,73 +2996,79 @@
       <c r="W45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
         <v>11800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>31400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>36500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
       <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
         <v>200</v>
-      </c>
-      <c r="R46" s="3">
-        <v>100</v>
       </c>
       <c r="S46" s="3">
         <v>100</v>
       </c>
       <c r="T46" s="3">
+        <v>100</v>
+      </c>
+      <c r="U46" s="3">
         <v>200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2997,38 +3102,41 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>34600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>34400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>34200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>60900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>66300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>66000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>65700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>65200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3059,11 +3167,11 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -3092,8 +3200,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3268,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3336,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3404,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3319,14 +3439,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -3343,8 +3463,8 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3352,8 +3472,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3540,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
         <v>11800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>24000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34700</v>
-      </c>
-      <c r="P54" s="3">
-        <v>34500</v>
       </c>
       <c r="Q54" s="3">
         <v>34500</v>
       </c>
       <c r="R54" s="3">
+        <v>34500</v>
+      </c>
+      <c r="S54" s="3">
         <v>61000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>66500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>66300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>65600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3636,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,62 +3662,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>400</v>
       </c>
       <c r="L57" s="3">
         <v>400</v>
       </c>
       <c r="M57" s="3">
+        <v>400</v>
+      </c>
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
@@ -3597,8 +3728,11 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3606,11 +3740,11 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>200</v>
+      </c>
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3623,8 +3757,8 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3662,47 +3796,50 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3718,8 +3855,8 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -3727,62 +3864,65 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
         <v>0</v>
       </c>
@@ -3792,8 +3932,11 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3831,20 +3974,20 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>2000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3857,46 +4000,49 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>600</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
       </c>
       <c r="I62" s="3">
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2200</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>2200</v>
@@ -3922,8 +4068,11 @@
       <c r="W62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4136,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4204,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,61 +4272,64 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E66" s="3">
         <v>10200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2300</v>
-      </c>
-      <c r="T66" s="3">
-        <v>2200</v>
       </c>
       <c r="U66" s="3">
         <v>2200</v>
@@ -4182,8 +4340,11 @@
       <c r="W66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4368,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4434,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4502,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4570,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4638,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-120700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-110200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-97800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-91200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-83100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-79500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-74200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-66800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-63100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-60900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-59300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-58300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4774,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4842,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4910,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>32300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>29600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>30100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>57800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>64200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>64000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>63700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>63400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,131 +5046,137 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44074</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43982</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43890</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43799</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43708</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43616</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>300</v>
       </c>
       <c r="U81" s="3">
         <v>300</v>
@@ -4992,8 +5187,11 @@
       <c r="W81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5215,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5082,8 +5281,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5349,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5417,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5485,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5553,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5621,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-4000</v>
       </c>
       <c r="H89" s="3">
         <v>-4000</v>
       </c>
       <c r="I89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J89" s="3">
         <v>-6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-200</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-100</v>
       </c>
       <c r="T89" s="3">
         <v>-100</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5717,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5562,8 +5783,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5851,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,8 +5919,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5727,38 +5957,41 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-200</v>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R94" s="3">
         <v>26800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5700</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6015,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6081,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6149,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6217,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,59 +6285,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>7800</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>31500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>38400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-26600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
@@ -6107,8 +6353,11 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,55 +6421,58 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8800</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-100</v>
       </c>
       <c r="S102" s="3">
         <v>-100</v>
@@ -6229,12 +6481,15 @@
         <v>-100</v>
       </c>
       <c r="U102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,111 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44074</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43982</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43890</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43799</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43708</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43616</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -827,8 +834,14 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -895,8 +908,14 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -963,8 +982,14 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,61 +1014,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F12" s="3">
         <v>8700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>9000</v>
       </c>
-      <c r="F12" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>6300</v>
-      </c>
       <c r="H12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J12" s="3">
         <v>2300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>5800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
         <v>0</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
@@ -1057,8 +1084,14 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,8 +1158,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1193,8 +1232,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1261,8 +1306,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,67 +1335,69 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F17" s="3">
         <v>10700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12100</v>
       </c>
-      <c r="F17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>7800</v>
-      </c>
       <c r="H17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J17" s="3">
         <v>3600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
-      </c>
-      <c r="U17" s="3">
-        <v>100</v>
-      </c>
-      <c r="V17" s="3">
-        <v>100</v>
       </c>
       <c r="W17" s="3">
         <v>100</v>
@@ -1352,8 +1405,14 @@
       <c r="X17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1361,58 +1420,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-12100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-7800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-100</v>
       </c>
       <c r="W18" s="3">
         <v>-100</v>
@@ -1420,8 +1479,14 @@
       <c r="X18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,8 +1511,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1455,67 +1522,73 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>200</v>
+      </c>
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>400</v>
       </c>
       <c r="W20" s="3">
         <v>400</v>
       </c>
       <c r="X20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1540,24 +1613,24 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-3700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1582,25 +1655,31 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>4</v>
@@ -1608,11 +1687,11 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1621,14 +1700,14 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1641,76 +1720,82 @@
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-12400</v>
       </c>
-      <c r="F23" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
-      </c>
-      <c r="U23" s="3">
-        <v>300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>300</v>
       </c>
       <c r="W23" s="3">
         <v>300</v>
@@ -1718,8 +1803,14 @@
       <c r="X23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1759,11 +1850,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>4</v>
@@ -1777,17 +1868,23 @@
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,67 +1951,73 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-12400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
-      </c>
-      <c r="U26" s="3">
-        <v>300</v>
-      </c>
-      <c r="V26" s="3">
-        <v>300</v>
       </c>
       <c r="W26" s="3">
         <v>300</v>
@@ -1922,67 +2025,73 @@
       <c r="X26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-12400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H27" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-7400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
-      </c>
-      <c r="U27" s="3">
-        <v>300</v>
-      </c>
-      <c r="V27" s="3">
-        <v>300</v>
       </c>
       <c r="W27" s="3">
         <v>300</v>
@@ -1990,8 +2099,14 @@
       <c r="X27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2173,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2247,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2321,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,8 +2395,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2271,126 +2410,132 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-400</v>
       </c>
       <c r="W32" s="3">
         <v>-400</v>
       </c>
       <c r="X32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-12400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H33" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-7400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
-      </c>
-      <c r="U33" s="3">
-        <v>300</v>
-      </c>
-      <c r="V33" s="3">
-        <v>300</v>
       </c>
       <c r="W33" s="3">
         <v>300</v>
@@ -2398,8 +2543,14 @@
       <c r="X33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,67 +2617,73 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-12400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H35" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-7400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
-      </c>
-      <c r="U35" s="3">
-        <v>300</v>
-      </c>
-      <c r="V35" s="3">
-        <v>300</v>
       </c>
       <c r="W35" s="3">
         <v>300</v>
@@ -2534,81 +2691,93 @@
       <c r="X35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44074</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43982</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43890</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43799</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43708</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43616</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2802,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,76 +2830,84 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>23400</v>
+      </c>
+      <c r="F41" s="3">
         <v>5000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>23200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>19400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>23400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>29700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>33500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>35800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8800</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2795,8 +2974,14 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2863,8 +3048,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2931,144 +3122,162 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>24000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>20600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>25300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>31400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>33900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>36500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>6700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8800</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3105,38 +3314,44 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>34600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>34400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>34200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>60900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>66300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>66000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>65700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>65200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3170,14 +3385,14 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3203,8 +3418,14 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3271,8 +3492,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3566,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,8 +3640,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3442,8 +3681,8 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3451,8 +3690,8 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>4</v>
@@ -3466,17 +3705,23 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,76 +3788,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>12900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>24000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>25300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>31400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>36500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>34700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>34500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>34500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>61000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>66500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>66300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>66000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>65600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3894,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,94 +3922,102 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F57" s="3">
         <v>5300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3760,11 +4027,11 @@
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3799,53 +4066,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F59" s="3">
         <v>7500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>800</v>
       </c>
       <c r="N59" s="3">
         <v>600</v>
       </c>
       <c r="O59" s="3">
+        <v>800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3858,85 +4131,97 @@
       <c r="U59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F60" s="3">
         <v>13000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6600</v>
       </c>
-      <c r="G60" s="3">
-        <v>6000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3600</v>
-      </c>
       <c r="I60" s="3">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="J60" s="3">
         <v>3600</v>
       </c>
       <c r="K60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="L60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3977,23 +4262,23 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>2000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4003,52 +4288,58 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>2200</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>2200</v>
@@ -4071,8 +4362,14 @@
       <c r="X62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4436,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4510,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,67 +4584,73 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18000</v>
+      </c>
+      <c r="F66" s="3">
         <v>13900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7100</v>
       </c>
-      <c r="G66" s="3">
-        <v>6600</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>2300</v>
-      </c>
-      <c r="U66" s="3">
-        <v>2200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>2200</v>
       </c>
       <c r="W66" s="3">
         <v>2200</v>
@@ -4343,8 +4658,14 @@
       <c r="X66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4690,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4760,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4834,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4908,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,76 +4982,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-141800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-134400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-120700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-110200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-97800</v>
       </c>
-      <c r="G72" s="3">
-        <v>-91200</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>-95100</v>
+      </c>
+      <c r="J72" s="3">
         <v>-83100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-79500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-74200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-66800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-63100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-60900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-59300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-58300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1000</v>
-      </c>
-      <c r="S72" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T72" s="3">
-        <v>1300</v>
       </c>
       <c r="U72" s="3">
         <v>1200</v>
       </c>
       <c r="V72" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X72" s="3">
         <v>900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +5130,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5204,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,76 +5278,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-8500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5800</v>
       </c>
-      <c r="G76" s="3">
-        <v>12300</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J76" s="3">
         <v>20400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>16100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>21400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>28700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>32300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>34500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>29600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>30100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>30600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>57800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>64200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>64000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>63700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>63400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,140 +5426,152 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44074</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43982</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43890</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43799</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43708</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43616</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-12400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-8100</v>
-      </c>
       <c r="H81" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-7400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
-      </c>
-      <c r="U81" s="3">
-        <v>300</v>
-      </c>
-      <c r="V81" s="3">
-        <v>300</v>
       </c>
       <c r="W81" s="3">
         <v>300</v>
@@ -5190,8 +5579,14 @@
       <c r="X81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5611,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5284,8 +5681,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5755,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5829,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5903,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5977,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,67 +6051,73 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-5300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-8000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
       </c>
       <c r="W89" s="3">
         <v>-100</v>
@@ -5692,8 +6125,14 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,8 +6157,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5786,8 +6227,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6301,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,8 +6375,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5960,38 +6419,44 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>26800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>5700</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6481,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6084,8 +6551,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6625,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6699,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,65 +6773,71 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>5200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>7800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>31500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>38400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-26600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-5500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -6356,8 +6847,14 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6424,72 +6921,84 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-7300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>30200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T102" s="3">
-        <v>-100</v>
       </c>
       <c r="U102" s="3">
         <v>-100</v>
       </c>
       <c r="V102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W102" s="3">
         <v>-100</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,118 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44074</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43982</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43890</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43799</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43708</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43616</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43524</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -840,8 +844,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,8 +921,11 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,64 +1029,65 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E12" s="3">
         <v>5800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
-        <v>9000</v>
-      </c>
       <c r="H12" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I12" s="3">
         <v>5500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1400</v>
-      </c>
-      <c r="O12" s="3">
-        <v>400</v>
       </c>
       <c r="P12" s="3">
         <v>400</v>
       </c>
       <c r="Q12" s="3">
+        <v>400</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
         <v>0</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+      <c r="U12" s="3">
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1181,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1238,8 +1258,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,70 +1363,71 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E17" s="3">
         <v>7900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10700</v>
       </c>
-      <c r="G17" s="3">
-        <v>12100</v>
-      </c>
       <c r="H17" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I17" s="3">
         <v>7000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200</v>
-      </c>
-      <c r="W17" s="3">
-        <v>100</v>
       </c>
       <c r="X17" s="3">
         <v>100</v>
@@ -1411,8 +1438,11 @@
       <c r="Z17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1420,61 +1450,61 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-10000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-100</v>
       </c>
       <c r="X18" s="3">
         <v>-100</v>
@@ -1485,8 +1515,11 @@
       <c r="Z18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1546,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1522,44 +1556,44 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>500</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1567,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>300</v>
       </c>
       <c r="V20" s="3">
         <v>300</v>
       </c>
       <c r="W20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X20" s="3">
         <v>400</v>
@@ -1585,18 +1619,21 @@
         <v>400</v>
       </c>
       <c r="Z20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
+      <c r="E21" s="3">
+        <v>-7400</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>4</v>
@@ -1619,21 +1656,21 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1661,19 +1698,22 @@
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1681,8 +1721,8 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
@@ -1693,8 +1733,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1706,11 +1746,11 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1726,8 +1766,8 @@
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1735,70 +1775,73 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H23" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
-      </c>
-      <c r="W23" s="3">
-        <v>300</v>
       </c>
       <c r="X23" s="3">
         <v>300</v>
@@ -1809,8 +1852,11 @@
       <c r="Z23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1856,8 +1902,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
@@ -1874,8 +1920,8 @@
       <c r="W24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,70 +2006,73 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10500</v>
       </c>
-      <c r="G26" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H26" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>300</v>
       </c>
       <c r="X26" s="3">
         <v>300</v>
@@ -2031,70 +2083,73 @@
       <c r="Z26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10500</v>
       </c>
-      <c r="G27" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H27" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>300</v>
       </c>
       <c r="X27" s="3">
         <v>300</v>
@@ -2105,8 +2160,11 @@
       <c r="Z27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2468,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2410,44 +2480,44 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2455,16 +2525,16 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-300</v>
       </c>
       <c r="V32" s="3">
         <v>-300</v>
       </c>
       <c r="W32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="X32" s="3">
         <v>-400</v>
@@ -2473,72 +2543,75 @@
         <v>-400</v>
       </c>
       <c r="Z32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H33" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100</v>
-      </c>
-      <c r="W33" s="3">
-        <v>300</v>
       </c>
       <c r="X33" s="3">
         <v>300</v>
@@ -2549,8 +2622,11 @@
       <c r="Z33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,70 +2699,73 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H35" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100</v>
-      </c>
-      <c r="W35" s="3">
-        <v>300</v>
       </c>
       <c r="X35" s="3">
         <v>300</v>
@@ -2697,87 +2776,93 @@
       <c r="Z35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44074</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43982</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43890</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43799</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43708</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43616</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43524</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
         <v>12000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8800</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
-      </c>
-      <c r="U41" s="3">
-        <v>100</v>
       </c>
       <c r="V41" s="3">
         <v>100</v>
       </c>
       <c r="W41" s="3">
+        <v>100</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
-      </c>
-      <c r="X41" s="3">
-        <v>300</v>
       </c>
       <c r="Y41" s="3">
         <v>300</v>
       </c>
       <c r="Z41" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,8 +3070,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3054,8 +3147,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3128,55 +3224,58 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
+      <c r="R45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -3185,16 +3284,16 @@
         <v>0</v>
       </c>
       <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
-      </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>100</v>
@@ -3202,82 +3301,88 @@
       <c r="Z45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8800</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
       <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
         <v>200</v>
-      </c>
-      <c r="U46" s="3">
-        <v>100</v>
       </c>
       <c r="V46" s="3">
         <v>100</v>
       </c>
       <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3320,38 +3425,41 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S47" s="3">
         <v>34600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>34400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>34200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>60900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>66300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>66000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>65700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>65200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3391,11 +3499,11 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -3424,8 +3532,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,31 +3763,34 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3687,14 +3807,14 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
@@ -3711,8 +3831,8 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E54" s="3">
         <v>13500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34700</v>
-      </c>
-      <c r="S54" s="3">
-        <v>34500</v>
       </c>
       <c r="T54" s="3">
         <v>34500</v>
       </c>
       <c r="U54" s="3">
+        <v>34500</v>
+      </c>
+      <c r="V54" s="3">
         <v>61000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>66500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>65600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,71 +4054,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>400</v>
       </c>
       <c r="P57" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
@@ -3998,29 +4129,32 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
         <v>700</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4033,8 +4167,8 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4072,56 +4206,59 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4137,8 +4274,8 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
@@ -4146,71 +4283,74 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E60" s="3">
         <v>14500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
       <c r="X60" s="3">
         <v>0</v>
       </c>
@@ -4220,8 +4360,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4268,20 +4411,20 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>2000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4294,55 +4437,58 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
       </c>
       <c r="I62" s="3">
         <v>600</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
       </c>
       <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2200</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S62" s="3">
         <v>2200</v>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,70 +4745,73 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E66" s="3">
         <v>14800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2300</v>
-      </c>
-      <c r="W66" s="3">
-        <v>2200</v>
       </c>
       <c r="X66" s="3">
         <v>2200</v>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-149600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-141800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-134400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-120700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-110200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-97800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-95100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-83100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-79500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-74200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-66800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-60900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-58300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-8500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>29600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>30100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>57800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>64200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>64000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>63700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,149 +5621,155 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44074</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43982</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43890</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43799</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43708</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43616</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43524</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H81" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100</v>
-      </c>
-      <c r="W81" s="3">
-        <v>300</v>
       </c>
       <c r="X81" s="3">
         <v>300</v>
@@ -5585,8 +5780,11 @@
       <c r="Z81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-4000</v>
       </c>
       <c r="K89" s="3">
         <v>-4000</v>
       </c>
       <c r="L89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M89" s="3">
         <v>-6300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-200</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-100</v>
       </c>
       <c r="W89" s="3">
         <v>-100</v>
       </c>
       <c r="X89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6608,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6425,38 +6655,41 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-200</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S94" s="3">
         <v>-200</v>
       </c>
       <c r="T94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U94" s="3">
         <v>26800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5700</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>4</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,68 +7022,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>27300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>5200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>7800</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>31500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>38400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-26600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5500</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -6853,8 +7099,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,64 +7176,67 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-100</v>
       </c>
       <c r="V102" s="3">
         <v>-100</v>
@@ -6993,12 +7245,15 @@
         <v>-100</v>
       </c>
       <c r="X102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,145 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44074</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43982</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43890</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43799</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43708</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43616</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43524</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -847,8 +851,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -924,8 +931,11 @@
       <c r="AA9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1011,11 @@
       <c r="AA10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,67 +1043,68 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E12" s="3">
         <v>5600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8500</v>
       </c>
-      <c r="G12" s="3">
-        <v>8700</v>
-      </c>
       <c r="H12" s="3">
-        <v>17200</v>
+        <v>9600</v>
       </c>
       <c r="I12" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
-      </c>
-      <c r="P12" s="3">
-        <v>400</v>
       </c>
       <c r="Q12" s="3">
         <v>400</v>
       </c>
       <c r="R12" s="3">
+        <v>400</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
       <c r="T12" s="3">
         <v>0</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
+      <c r="V12" s="3">
+        <v>0</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>4</v>
@@ -1107,8 +1121,11 @@
       <c r="AA12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,31 +1201,34 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1261,8 +1281,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1361,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,73 +1390,74 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E17" s="3">
         <v>8100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10000</v>
       </c>
-      <c r="G17" s="3">
-        <v>10700</v>
-      </c>
       <c r="H17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I17" s="3">
         <v>11300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
-      </c>
-      <c r="X17" s="3">
-        <v>100</v>
       </c>
       <c r="Y17" s="3">
         <v>100</v>
@@ -1441,73 +1468,76 @@
       <c r="AA17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-8500</v>
       </c>
       <c r="E18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-11300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-100</v>
       </c>
       <c r="Y18" s="3">
         <v>-100</v>
@@ -1518,8 +1548,11 @@
       <c r="AA18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,56 +1580,57 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>200</v>
+      </c>
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1604,16 +1638,16 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>300</v>
       </c>
       <c r="W20" s="3">
         <v>300</v>
       </c>
       <c r="X20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>400</v>
@@ -1622,33 +1656,36 @@
         <v>400</v>
       </c>
       <c r="AA20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-8400</v>
       </c>
       <c r="E21" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-7900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1659,21 +1696,21 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1701,8 +1738,11 @@
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1712,8 +1752,8 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1724,8 +1764,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1736,8 +1776,8 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1749,11 +1789,11 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>1500</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1769,8 +1809,8 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1778,73 +1818,76 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H23" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I23" s="3">
         <v>-11700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
-      </c>
-      <c r="X23" s="3">
-        <v>300</v>
       </c>
       <c r="Y23" s="3">
         <v>300</v>
@@ -1855,13 +1898,16 @@
       <c r="AA23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1905,8 +1951,8 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
@@ -1923,8 +1969,8 @@
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -1932,8 +1978,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,73 +2058,76 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H26" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I26" s="3">
         <v>-11700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>300</v>
       </c>
       <c r="Y26" s="3">
         <v>300</v>
@@ -2086,73 +2138,76 @@
       <c r="AA26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H27" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I27" s="3">
         <v>-11700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
-      </c>
-      <c r="X27" s="3">
-        <v>300</v>
       </c>
       <c r="Y27" s="3">
         <v>300</v>
@@ -2163,8 +2218,11 @@
       <c r="AA27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2298,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2378,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2458,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,56 +2538,59 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2528,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-300</v>
       </c>
       <c r="W32" s="3">
         <v>-300</v>
       </c>
       <c r="X32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>-400</v>
@@ -2546,75 +2616,78 @@
         <v>-400</v>
       </c>
       <c r="AA32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H33" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I33" s="3">
         <v>-11700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
-      </c>
-      <c r="X33" s="3">
-        <v>300</v>
       </c>
       <c r="Y33" s="3">
         <v>300</v>
@@ -2625,8 +2698,11 @@
       <c r="AA33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,73 +2778,76 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H35" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I35" s="3">
         <v>-11700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
-      </c>
-      <c r="X35" s="3">
-        <v>300</v>
       </c>
       <c r="Y35" s="3">
         <v>300</v>
@@ -2779,90 +2858,96 @@
       <c r="AA35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44074</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43982</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43890</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43799</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43708</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43616</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43524</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2975,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3005,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8800</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>200</v>
-      </c>
-      <c r="V41" s="3">
-        <v>100</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
       </c>
       <c r="X41" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>300</v>
       </c>
       <c r="Z41" s="3">
         <v>300</v>
       </c>
       <c r="AA41" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,31 +3163,34 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3150,31 +3243,34 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3227,58 +3323,61 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="I45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="S45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3287,16 +3386,16 @@
         <v>0</v>
       </c>
       <c r="V45" s="3">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
         <v>100</v>
@@ -3304,108 +3403,114 @@
       <c r="AA45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>33900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>36500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8800</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
       <c r="T46" s="3">
         <v>0</v>
       </c>
       <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
         <v>200</v>
-      </c>
-      <c r="V46" s="3">
-        <v>100</v>
       </c>
       <c r="W46" s="3">
         <v>100</v>
       </c>
       <c r="X46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="3">
         <v>200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3428,61 +3533,64 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T47" s="3">
         <v>34600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>34400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>34200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>60900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>66300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>66000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>65700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>65200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3502,11 +3610,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -3535,8 +3643,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3723,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3803,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,16 +3883,19 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="E52" s="3">
+        <v>800</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>4</v>
@@ -3792,8 +3912,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3810,14 +3930,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
@@ -3834,8 +3954,8 @@
       <c r="X52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3843,8 +3963,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4043,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E54" s="3">
         <v>8100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>36500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34700</v>
-      </c>
-      <c r="T54" s="3">
-        <v>34500</v>
       </c>
       <c r="U54" s="3">
         <v>34500</v>
       </c>
       <c r="V54" s="3">
+        <v>34500</v>
+      </c>
+      <c r="W54" s="3">
         <v>61000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>66500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>66300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>66000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>65600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4155,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,74 +4185,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>400</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
@@ -4132,32 +4263,35 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4170,8 +4304,8 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4209,59 +4343,62 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>9000</v>
       </c>
-      <c r="E59" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>13300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>7500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4277,8 +4414,8 @@
       <c r="X59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4286,74 +4423,77 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E60" s="3">
         <v>13900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
       <c r="Y60" s="3">
         <v>0</v>
       </c>
@@ -4363,8 +4503,11 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4414,20 +4557,20 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4440,58 +4583,61 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>600</v>
       </c>
       <c r="J62" s="3">
         <v>600</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2200</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T62" s="3">
         <v>2200</v>
@@ -4517,8 +4663,11 @@
       <c r="AA62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4743,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4823,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,73 +4903,76 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E66" s="3">
         <v>14100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2300</v>
-      </c>
-      <c r="X66" s="3">
-        <v>2200</v>
       </c>
       <c r="Y66" s="3">
         <v>2200</v>
@@ -4825,8 +4983,11 @@
       <c r="AA66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5015,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5093,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5173,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5253,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5333,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-158000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-149600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-141800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-134400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-120700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-110200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-97800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-95100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-83100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-79500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-74200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-66800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-63100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-59300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-58300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5493,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5573,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5653,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-6000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-8500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>30100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>30600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>57800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>64200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>64000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,155 +5813,161 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44074</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43982</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43890</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43799</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43708</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43616</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43524</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
-        <v>-10500</v>
-      </c>
       <c r="H81" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="I81" s="3">
         <v>-11700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
-      </c>
-      <c r="X81" s="3">
-        <v>300</v>
       </c>
       <c r="Y81" s="3">
         <v>300</v>
@@ -5783,8 +5978,11 @@
       <c r="AA81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,31 +6010,32 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5889,8 +6088,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6168,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6248,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6328,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6408,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6488,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-4000</v>
       </c>
       <c r="L89" s="3">
         <v>-4000</v>
       </c>
       <c r="M89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="N89" s="3">
         <v>-6300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-200</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-100</v>
       </c>
       <c r="X89" s="3">
         <v>-100</v>
       </c>
       <c r="Y89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,31 +6600,32 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6457,8 +6678,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6758,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,31 +6838,34 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6658,38 +6888,41 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-200</v>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>-200</v>
       </c>
       <c r="U94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V94" s="3">
         <v>26800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5700</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>4</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,31 +6950,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6794,8 +7028,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7108,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7188,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,71 +7268,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>2700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>27300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>5200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>7800</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>31500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>38400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-26600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -7102,31 +7348,34 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7179,67 +7428,70 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8800</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
-      </c>
-      <c r="V102" s="3">
-        <v>-100</v>
       </c>
       <c r="W102" s="3">
         <v>-100</v>
@@ -7248,12 +7500,15 @@
         <v>-100</v>
       </c>
       <c r="Y102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,126 +656,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44165</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44074</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43982</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43890</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43799</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43708</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43616</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43524</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,11 +807,11 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -854,8 +861,14 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -934,8 +947,14 @@
       <c r="AB9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1014,8 +1033,14 @@
       <c r="AB10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,73 +1069,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>5600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>5800</v>
       </c>
-      <c r="G12" s="3">
-        <v>8500</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J12" s="3">
         <v>9600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>8300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>10200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
       <c r="V12" s="3">
         <v>0</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>4</v>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>4</v>
@@ -1124,8 +1151,14 @@
       <c r="AB12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,8 +1237,14 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1230,11 +1269,11 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1284,8 +1323,14 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1364,8 +1409,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,79 +1442,81 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F17" s="3">
         <v>8500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7900</v>
       </c>
-      <c r="G17" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J17" s="3">
         <v>11600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>11300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>200</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>100</v>
       </c>
       <c r="AA17" s="3">
         <v>100</v>
@@ -1471,79 +1524,85 @@
       <c r="AB17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-8100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-11600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-7000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-11700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-100</v>
       </c>
       <c r="AA18" s="3">
         <v>-100</v>
@@ -1551,8 +1610,14 @@
       <c r="AB18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,8 +1646,10 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1590,133 +1657,139 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>400</v>
       </c>
       <c r="AA20" s="3">
         <v>400</v>
       </c>
       <c r="AB20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-7600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J21" s="3">
         <v>-11400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-11800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-3700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1741,8 +1814,14 @@
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1767,11 +1846,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1779,11 +1858,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1792,14 +1871,14 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>1500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1812,88 +1891,94 @@
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-7400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-11300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-11700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>100</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>300</v>
       </c>
       <c r="AA23" s="3">
         <v>300</v>
@@ -1901,19 +1986,25 @@
       <c r="AB23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1954,11 +2045,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>4</v>
@@ -1972,17 +2063,23 @@
       <c r="Y24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,79 +2158,85 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-7400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-11300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-11700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>300</v>
       </c>
       <c r="AA26" s="3">
         <v>300</v>
@@ -2141,79 +2244,85 @@
       <c r="AB26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-7400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-11300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>300</v>
       </c>
       <c r="AA27" s="3">
         <v>300</v>
@@ -2221,8 +2330,14 @@
       <c r="AB27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2416,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2502,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2588,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,8 +2674,14 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2550,150 +2689,156 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-400</v>
       </c>
       <c r="AA32" s="3">
         <v>-400</v>
       </c>
       <c r="AB32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J33" s="3">
         <v>-11300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-11700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>300</v>
       </c>
       <c r="AA33" s="3">
         <v>300</v>
@@ -2701,8 +2846,14 @@
       <c r="AB33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,79 +2932,85 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J35" s="3">
         <v>-11300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-11700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>300</v>
       </c>
       <c r="AA35" s="3">
         <v>300</v>
@@ -2861,93 +3018,105 @@
       <c r="AB35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44165</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44074</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43982</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43890</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43799</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43708</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43616</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43524</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3145,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,88 +3177,96 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F41" s="3">
         <v>5600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>23400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>18500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>23200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>19400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>23400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>29700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>33500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>35800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8800</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,8 +3345,14 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3192,11 +3377,11 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3246,8 +3431,14 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3272,11 +3463,11 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3326,8 +3517,14 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3352,142 +3549,154 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
       <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
       <c r="Z45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F46" s="3">
         <v>6800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>23700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>18900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>24000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>20600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>25300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>31400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>33900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>36500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>8800</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
       <c r="V46" s="3">
+        <v>0</v>
+      </c>
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
         <v>200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3512,11 +3721,11 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3536,38 +3745,44 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V47" s="3">
         <v>34600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>34400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>34200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>60900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>66300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>66000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>65700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>65200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3592,11 +3807,11 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3613,14 +3828,14 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3646,8 +3861,14 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3726,8 +3947,14 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +4033,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,8 +4119,14 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3897,11 +4136,11 @@
       <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
+      <c r="F52" s="3">
+        <v>800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>800</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
@@ -3915,11 +4154,11 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3933,8 +4172,8 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3942,8 +4181,8 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>4</v>
@@ -3957,17 +4196,23 @@
       <c r="Y52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,88 +4291,100 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F54" s="3">
         <v>7600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>23700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>24000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>20600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>25300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>31400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>33900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>36500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>34700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>34500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>34500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>61000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>66500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>66300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>66000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>65600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4413,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,118 +4445,126 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F57" s="3">
         <v>8800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4307,11 +4574,11 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4346,16 +4613,22 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
@@ -4363,48 +4636,48 @@
       <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+      <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>400</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>9000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
-      </c>
-      <c r="P59" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>800</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>800</v>
+      </c>
+      <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4417,97 +4690,109 @@
       <c r="Y59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F60" s="3">
         <v>17500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>13900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M60" s="3">
-        <v>4500</v>
       </c>
       <c r="N60" s="3">
         <v>3600</v>
       </c>
       <c r="O60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="P60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>0</v>
-      </c>
       <c r="AA60" s="3">
         <v>0</v>
       </c>
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4560,23 +4845,23 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>2000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4586,64 +4871,70 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="U62" s="3">
-        <v>2200</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>2200</v>
@@ -4666,8 +4957,14 @@
       <c r="AB62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +5043,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +5129,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,79 +5215,85 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14700</v>
+      </c>
+      <c r="F66" s="3">
         <v>17600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>18000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>10200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>5000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>3300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>2200</v>
       </c>
       <c r="AA66" s="3">
         <v>2200</v>
@@ -4986,8 +5301,14 @@
       <c r="AB66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5337,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5419,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5505,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5256,8 +5591,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,88 +5677,100 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-170700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-164300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-158000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-149600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-141800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-134400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-120700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-110200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-97800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-95100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-83100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-79500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-74200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-66800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-63100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-60900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-59300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-58300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1000</v>
-      </c>
-      <c r="W72" s="3">
-        <v>1200</v>
-      </c>
-      <c r="X72" s="3">
-        <v>1300</v>
       </c>
       <c r="Y72" s="3">
         <v>1200</v>
       </c>
       <c r="Z72" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB72" s="3">
         <v>900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5849,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5935,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,88 +6021,100 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-10000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-6000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-1300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-8500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>21400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>28700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>32300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>34500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>29600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>30100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>30600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>57800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>64200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>64000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>63700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>63400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,164 +6193,176 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44165</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44074</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43982</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43890</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43799</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43708</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43616</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43524</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J81" s="3">
         <v>-11300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-11700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>300</v>
       </c>
       <c r="AA81" s="3">
         <v>300</v>
@@ -5981,8 +6370,14 @@
       <c r="AB81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,8 +6406,10 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6037,11 +6434,11 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6091,8 +6488,14 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6574,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6660,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6746,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6832,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,79 +6918,85 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-8900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
       </c>
       <c r="AA89" s="3">
         <v>-100</v>
@@ -6571,8 +7004,14 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,8 +7040,10 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6627,11 +7068,11 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6681,8 +7122,14 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +7208,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,8 +7294,14 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6867,11 +7326,11 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -6891,38 +7350,44 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>26800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>5700</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7416,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6977,11 +7444,11 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7031,8 +7498,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7584,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7670,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,77 +7756,83 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>27300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>5200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>7800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>31500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>38400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-26600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-5500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -7351,8 +7842,14 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7377,11 +7874,11 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7431,84 +7928,96 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-11400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>18400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>30200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
-      </c>
-      <c r="W102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X102" s="3">
-        <v>-100</v>
       </c>
       <c r="Y102" s="3">
         <v>-100</v>
       </c>
       <c r="Z102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA102" s="3">
         <v>-100</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RVPH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>RVPH</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44165</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44074</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43982</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43890</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43799</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43708</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43616</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43524</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -813,8 +817,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -867,8 +871,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,8 +960,11 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1039,8 +1049,11 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,76 +1084,77 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E12" s="3">
         <v>4100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>400</v>
       </c>
       <c r="T12" s="3">
         <v>400</v>
       </c>
       <c r="U12" s="3">
+        <v>400</v>
+      </c>
+      <c r="V12" s="3">
         <v>300</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
       <c r="W12" s="3">
         <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>0</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>4</v>
+      <c r="Y12" s="3">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>4</v>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,8 +1260,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1275,8 +1295,8 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1329,8 +1349,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,82 +1470,83 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>200</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>100</v>
       </c>
       <c r="AB17" s="3">
         <v>100</v>
@@ -1530,82 +1557,85 @@
       <c r="AD17" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-100</v>
       </c>
       <c r="AB18" s="3">
         <v>-100</v>
@@ -1616,8 +1646,11 @@
       <c r="AD18" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,8 +1681,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1663,50 +1697,50 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1714,16 +1748,16 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>300</v>
       </c>
       <c r="Z20" s="3">
         <v>300</v>
       </c>
       <c r="AA20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AB20" s="3">
         <v>400</v>
@@ -1732,43 +1766,46 @@
         <v>400</v>
       </c>
       <c r="AD20" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1778,21 +1815,21 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1820,8 +1857,11 @@
       <c r="AD21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1852,8 +1892,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1864,8 +1904,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1877,11 +1917,11 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>1500</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1897,8 +1937,8 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1906,82 +1946,85 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>100</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>300</v>
       </c>
       <c r="AB23" s="3">
         <v>300</v>
@@ -1992,8 +2035,11 @@
       <c r="AD23" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2003,11 +2049,11 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -2051,8 +2097,8 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>4</v>
@@ -2069,8 +2115,8 @@
       <c r="AA24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2078,8 +2124,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,82 +2213,85 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>100</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>300</v>
       </c>
       <c r="AB26" s="3">
         <v>300</v>
@@ -2250,82 +2302,85 @@
       <c r="AD26" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>300</v>
       </c>
       <c r="AB27" s="3">
         <v>300</v>
@@ -2336,8 +2391,11 @@
       <c r="AD27" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,8 +2747,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2695,50 +2765,50 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2746,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-300</v>
       </c>
       <c r="Z32" s="3">
         <v>-300</v>
       </c>
       <c r="AA32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="AB32" s="3">
         <v>-400</v>
@@ -2764,84 +2834,87 @@
         <v>-400</v>
       </c>
       <c r="AD32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>300</v>
       </c>
       <c r="AB33" s="3">
         <v>300</v>
@@ -2852,8 +2925,11 @@
       <c r="AD33" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,82 +3014,85 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>300</v>
       </c>
       <c r="AB35" s="3">
         <v>300</v>
@@ -3024,99 +3103,105 @@
       <c r="AD35" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44165</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44074</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43982</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43890</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43799</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43708</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43616</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43524</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3265,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8800</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
         <v>0</v>
       </c>
       <c r="X41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
         <v>200</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>100</v>
       </c>
       <c r="Z41" s="3">
         <v>100</v>
       </c>
       <c r="AA41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB41" s="3">
         <v>200</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>300</v>
       </c>
       <c r="AC41" s="3">
         <v>300</v>
       </c>
       <c r="AD41" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE41" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3351,8 +3441,11 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3383,8 +3476,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3437,8 +3530,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3469,8 +3565,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3523,8 +3619,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3555,35 +3654,35 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3592,16 +3691,16 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
       <c r="AB45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="3">
         <v>100</v>
@@ -3609,94 +3708,100 @@
       <c r="AD45" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E46" s="3">
         <v>6300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8800</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
       <c r="W46" s="3">
         <v>0</v>
       </c>
       <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
         <v>200</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>100</v>
       </c>
       <c r="Z46" s="3">
         <v>100</v>
       </c>
       <c r="AA46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB46" s="3">
         <v>200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3727,8 +3832,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3751,38 +3856,41 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W47" s="3">
         <v>34600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>34400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>34200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>60900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>66300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>66000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>65700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>65200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>64900</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3813,8 +3921,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3834,11 +3942,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3867,8 +3975,11 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,8 +4242,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4142,8 +4262,8 @@
       <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>800</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -4160,8 +4280,8 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -4178,14 +4298,14 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>4</v>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
@@ -4202,8 +4322,8 @@
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E54" s="3">
         <v>7100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>36500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34700</v>
-      </c>
-      <c r="W54" s="3">
-        <v>34500</v>
       </c>
       <c r="X54" s="3">
         <v>34500</v>
       </c>
       <c r="Y54" s="3">
+        <v>34500</v>
+      </c>
+      <c r="Z54" s="3">
         <v>61000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>66300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>66000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>65600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,83 +4577,84 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
-      </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
@@ -4533,41 +4664,44 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
@@ -4580,8 +4714,8 @@
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4619,19 +4753,22 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
       </c>
       <c r="F59" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
@@ -4642,8 +4779,8 @@
       <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>400</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -4651,36 +4788,36 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4696,8 +4833,8 @@
       <c r="AA59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -4705,83 +4842,86 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E60" s="3">
         <v>11500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>100</v>
       </c>
-      <c r="AA60" s="3">
-        <v>0</v>
-      </c>
       <c r="AB60" s="3">
         <v>0</v>
       </c>
@@ -4791,8 +4931,11 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4851,20 +4994,20 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -4877,8 +5020,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4886,58 +5032,58 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
       </c>
       <c r="G62" s="3">
+        <v>100</v>
+      </c>
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
       </c>
       <c r="M62" s="3">
         <v>600</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
       </c>
       <c r="P62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V62" s="3">
-        <v>2200</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>2200</v>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,82 +5376,85 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>2200</v>
       </c>
       <c r="AB66" s="3">
         <v>2200</v>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3">
         <v>2200</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-176800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-170700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-164300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-158000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-149600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-141800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-134400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-120700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-110200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-97800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-95100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-83100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-79500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-74200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-66800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-63100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-60900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-59300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-58300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-4500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-6000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-8500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>32300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>29600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>30100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>30600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>57800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>63700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>63400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>63100</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,173 +6388,179 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44165</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44074</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43982</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43890</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43799</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43708</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43616</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43524</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43434</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>300</v>
       </c>
       <c r="AB81" s="3">
         <v>300</v>
@@ -6376,8 +6571,11 @@
       <c r="AD81" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,8 +6606,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6440,8 +6639,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-4000</v>
       </c>
       <c r="O89" s="3">
         <v>-4000</v>
       </c>
       <c r="P89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-100</v>
       </c>
       <c r="AA89" s="3">
         <v>-100</v>
       </c>
       <c r="AB89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,8 +7262,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7074,8 +7295,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7527,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7332,8 +7562,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7356,38 +7586,41 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-200</v>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W94" s="3">
         <v>-200</v>
       </c>
       <c r="X94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y94" s="3">
         <v>26800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5700</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>4</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7651,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7450,8 +7684,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,80 +8005,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>17000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>27300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>5200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>7800</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>31500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>38400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -7848,8 +8094,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7880,8 +8129,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7934,76 +8183,79 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>18400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8800</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>-100</v>
       </c>
       <c r="Z102" s="3">
         <v>-100</v>
@@ -8012,12 +8264,15 @@
         <v>-100</v>
       </c>
       <c r="AB102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>
